--- a/data/trans_orig/P3A_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251118</t>
+          <t>252130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265638</t>
+          <t>265686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246190</t>
+          <t>246030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257504</t>
+          <t>257556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>504066</t>
+          <t>501833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>521819</t>
+          <t>520572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50638</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463643</t>
+          <t>463009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482559</t>
+          <t>482349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475772</t>
+          <t>476821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493873</t>
+          <t>493850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946386</t>
+          <t>945665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972139</t>
+          <t>971923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>38601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297239</t>
+          <t>297579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311120</t>
+          <t>311213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312630</t>
+          <t>312955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327988</t>
+          <t>327962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615104</t>
+          <t>615657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635557</t>
+          <t>635621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44023</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336970</t>
+          <t>337203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>351990</t>
+          <t>352052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340628</t>
+          <t>339866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357767</t>
+          <t>357969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684951</t>
+          <t>684706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706502</t>
+          <t>705739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189651</t>
+          <t>189788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200657</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200872</t>
+          <t>199251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394991</t>
+          <t>394225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406801</t>
+          <t>407060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249417</t>
+          <t>250029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264164</t>
+          <t>264226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267846</t>
+          <t>267211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277108</t>
+          <t>276974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523433</t>
+          <t>522374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539064</t>
+          <t>538835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>52076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584605</t>
+          <t>584330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>602627</t>
+          <t>602517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607185</t>
+          <t>606826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>625334</t>
+          <t>625420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1199658</t>
+          <t>1198786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1224279</t>
+          <t>1223093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26600</t>
+          <t>26157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>46804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79840</t>
+          <t>78253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693195</t>
+          <t>692727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>716313</t>
+          <t>716756</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>745916</t>
+          <t>746242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>766630</t>
+          <t>766943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1446584</t>
+          <t>1448171</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1478737</t>
+          <t>1479620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110225</t>
+          <t>111528</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156128</t>
+          <t>161196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87566</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>128710</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211408</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>271328</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3119533</t>
+          <t>3114465</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3165436</t>
+          <t>3164133</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3245935</t>
+          <t>3248379</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3287079</t>
+          <t>3288439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6378979</t>
+          <t>6380530</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6438899</t>
+          <t>6440921</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21573</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280021</t>
+          <t>279951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291193</t>
+          <t>291239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265672</t>
+          <t>266941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280771</t>
+          <t>281014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551487</t>
+          <t>551547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>569896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>36454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>50502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484155</t>
+          <t>482397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499309</t>
+          <t>498425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487899</t>
+          <t>487311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508362</t>
+          <t>509307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977818</t>
+          <t>977731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004165</t>
+          <t>1002936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51630</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>294656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311939</t>
+          <t>312069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313352</t>
+          <t>314000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330543</t>
+          <t>330867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613436</t>
+          <t>613898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639000</t>
+          <t>639787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36334</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>354163</t>
+          <t>353575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368701</t>
+          <t>367901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366889</t>
+          <t>365918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381806</t>
+          <t>380852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726599</t>
+          <t>725694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747938</t>
+          <t>746092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192567</t>
+          <t>192780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207224</t>
+          <t>207307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201094</t>
+          <t>201058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214496</t>
+          <t>214417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400392</t>
+          <t>400600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418850</t>
+          <t>419470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>51335</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236652</t>
+          <t>236827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257680</t>
+          <t>255648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>259697</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273699</t>
+          <t>273713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502885</t>
+          <t>502677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526910</t>
+          <t>527442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>50107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40693</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>75746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630427</t>
+          <t>630241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650453</t>
+          <t>651101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642651</t>
+          <t>643746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>669863</t>
+          <t>668932</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282562</t>
+          <t>1280895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315948</t>
+          <t>1314855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>50226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46824</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78476</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743616</t>
+          <t>744086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763597</t>
+          <t>762917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>773072</t>
+          <t>771626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>797549</t>
+          <t>795567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1522474</t>
+          <t>1522138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554126</t>
+          <t>1554093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>154617</t>
+          <t>156295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>135629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>192863</t>
+          <t>188487</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>260008</t>
+          <t>261714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>327290</t>
+          <t>328811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3271102</t>
+          <t>3269424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3317986</t>
+          <t>3318599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3363445</t>
+          <t>3367821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3416595</t>
+          <t>3420679</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6654737</t>
+          <t>6653216</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6722019</t>
+          <t>6720313</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279119</t>
+          <t>279294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290525</t>
+          <t>290315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270819</t>
+          <t>269855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285060</t>
+          <t>284730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555198</t>
+          <t>555986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572845</t>
+          <t>574225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12851</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486008</t>
+          <t>485507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496096</t>
+          <t>495788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500318</t>
+          <t>500898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516985</t>
+          <t>516458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>989795</t>
+          <t>991109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009824</t>
+          <t>1010189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303088</t>
+          <t>302298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313914</t>
+          <t>313790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323512</t>
+          <t>323614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334165</t>
+          <t>334172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631704</t>
+          <t>631285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646027</t>
+          <t>646145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358067</t>
+          <t>357563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366419</t>
+          <t>366420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363054</t>
+          <t>364160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381897</t>
+          <t>381838</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726842</t>
+          <t>728118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746640</t>
+          <t>746520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204231</t>
+          <t>204236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208721</t>
+          <t>208271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216722</t>
+          <t>216717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417259</t>
+          <t>418483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426924</t>
+          <t>427004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247434</t>
+          <t>248195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258005</t>
+          <t>258339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247387</t>
+          <t>246965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264671</t>
+          <t>263560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501767</t>
+          <t>501309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519983</t>
+          <t>520028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39846</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>37208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67200</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618859</t>
+          <t>618763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640633</t>
+          <t>639980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>649416</t>
+          <t>650395</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671823</t>
+          <t>671516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277570</t>
+          <t>1277037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307611</t>
+          <t>1307562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>33947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>62177</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744768</t>
+          <t>744890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764282</t>
+          <t>763626</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>790294</t>
+          <t>788497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811347</t>
+          <t>810490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1541571</t>
+          <t>1542573</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570557</t>
+          <t>1570803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>64369</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101792</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>87941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>162745</t>
+          <t>158996</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>220265</t>
+          <t>218791</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3283517</t>
+          <t>3284313</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3319009</t>
+          <t>3320940</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3407457</t>
+          <t>3406804</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3454645</t>
+          <t>3451639</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6704625</t>
+          <t>6706099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6762145</t>
+          <t>6765894</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288427</t>
+          <t>289033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302509</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266911</t>
+          <t>266493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278951</t>
+          <t>278430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560961</t>
+          <t>560635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578396</t>
+          <t>578258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>29152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53944</t>
+          <t>55134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489186</t>
+          <t>489238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508529</t>
+          <t>508713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482416</t>
+          <t>482146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497350</t>
+          <t>497004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>979415</t>
+          <t>978225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1001865</t>
+          <t>1002847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14277</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285350</t>
+          <t>285828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301141</t>
+          <t>301133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305493</t>
+          <t>306895</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323267</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598933</t>
+          <t>598536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620772</t>
+          <t>621092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>35350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67857</t>
+          <t>68473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271859</t>
+          <t>272662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295831</t>
+          <t>295591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440381</t>
+          <t>440368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460533</t>
+          <t>460869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720417</t>
+          <t>719801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>751490</t>
+          <t>752918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>168472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175350</t>
+          <t>175456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245837</t>
+          <t>245077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254620</t>
+          <t>254330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>416725</t>
+          <t>415551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428118</t>
+          <t>427487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17826</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31462</t>
+          <t>31648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247545</t>
+          <t>246363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257962</t>
+          <t>257812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225594</t>
+          <t>225408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239230</t>
+          <t>239247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>475926</t>
+          <t>477624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>493695</t>
+          <t>494009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>51532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60365</t>
+          <t>61554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98701</t>
+          <t>101848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572612</t>
+          <t>572747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>600316</t>
+          <t>599251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>788900</t>
+          <t>787711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>829359</t>
+          <t>829749</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1374843</t>
+          <t>1371696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1427499</t>
+          <t>1424152</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>52075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907109</t>
+          <t>905873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923683</t>
+          <t>923639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>684708</t>
+          <t>684051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699544</t>
+          <t>699305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1595922</t>
+          <t>1594377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1623948</t>
+          <t>1622417</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115754</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179417</t>
+          <t>174998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223279</t>
+          <t>225152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>303718</t>
+          <t>299741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>390597</t>
+          <t>389766</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3279301</t>
+          <t>3283720</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342964</t>
+          <t>3343119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3487741</t>
+          <t>3485868</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3545555</t>
+          <t>3553967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6779141</t>
+          <t>6779972</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6866020</t>
+          <t>6869997</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>251798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265686</t>
+          <t>265337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246030</t>
+          <t>246791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257556</t>
+          <t>257501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501833</t>
+          <t>503093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520572</t>
+          <t>520753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>50321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463009</t>
+          <t>463541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482349</t>
+          <t>482241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476821</t>
+          <t>477309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493850</t>
+          <t>493895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945665</t>
+          <t>946703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971923</t>
+          <t>972862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>37569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297579</t>
+          <t>297143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311213</t>
+          <t>311224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312955</t>
+          <t>312878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327962</t>
+          <t>327851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615657</t>
+          <t>616689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635621</t>
+          <t>636065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337203</t>
+          <t>337489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352052</t>
+          <t>351227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339866</t>
+          <t>341239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357969</t>
+          <t>357671</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684706</t>
+          <t>685211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>705739</t>
+          <t>706765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189788</t>
+          <t>189582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200596</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199251</t>
+          <t>201174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394225</t>
+          <t>394772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407060</t>
+          <t>406701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>26957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250029</t>
+          <t>250386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264226</t>
+          <t>264102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267211</t>
+          <t>268755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276974</t>
+          <t>277108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>522374</t>
+          <t>521998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538835</t>
+          <t>538593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52076</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584330</t>
+          <t>584901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>602517</t>
+          <t>603456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606826</t>
+          <t>607240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>625420</t>
+          <t>624818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1198786</t>
+          <t>1200183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1223093</t>
+          <t>1224107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26157</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46804</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>77823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692727</t>
+          <t>692088</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>716756</t>
+          <t>717033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746242</t>
+          <t>747717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>766943</t>
+          <t>766925</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1448171</t>
+          <t>1448601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1479620</t>
+          <t>1480200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111528</t>
+          <t>111755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161196</t>
+          <t>157176</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86834</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126266</t>
+          <t>128260</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>209386</t>
+          <t>211271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>269777</t>
+          <t>270028</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3114465</t>
+          <t>3118485</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3164133</t>
+          <t>3163906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3248379</t>
+          <t>3246385</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3288439</t>
+          <t>3287811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6380530</t>
+          <t>6380279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6440921</t>
+          <t>6439036</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279951</t>
+          <t>280284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291239</t>
+          <t>291012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266941</t>
+          <t>265550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281014</t>
+          <t>280843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551547</t>
+          <t>551654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569896</t>
+          <t>570011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50502</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482397</t>
+          <t>481852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498425</t>
+          <t>498495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487311</t>
+          <t>487506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509307</t>
+          <t>508409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977731</t>
+          <t>979367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002936</t>
+          <t>1003691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>29623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27020</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>50173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294656</t>
+          <t>294423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312069</t>
+          <t>311982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314000</t>
+          <t>313161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330867</t>
+          <t>331060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613898</t>
+          <t>614893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639787</t>
+          <t>638410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353575</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367901</t>
+          <t>367424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365918</t>
+          <t>366451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380852</t>
+          <t>381867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725694</t>
+          <t>726132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746092</t>
+          <t>746048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192780</t>
+          <t>192439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207307</t>
+          <t>207482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201058</t>
+          <t>201735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214417</t>
+          <t>214496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400600</t>
+          <t>400559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>419470</t>
+          <t>419067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>27113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51335</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236827</t>
+          <t>236989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255648</t>
+          <t>257338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>259488</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273713</t>
+          <t>273894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502677</t>
+          <t>503392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527442</t>
+          <t>526899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>32225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50107</t>
+          <t>49556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>40861</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75746</t>
+          <t>74256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630241</t>
+          <t>630563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651101</t>
+          <t>650185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>643746</t>
+          <t>644297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>668932</t>
+          <t>670227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1280895</t>
+          <t>1282385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1314855</t>
+          <t>1315780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26285</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50226</t>
+          <t>49036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744086</t>
+          <t>742946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762917</t>
+          <t>762444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>771626</t>
+          <t>772816</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>795567</t>
+          <t>797715</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1522138</t>
+          <t>1523531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1554093</t>
+          <t>1553889</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107120</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>135337</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188487</t>
+          <t>187871</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>261714</t>
+          <t>256649</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>328811</t>
+          <t>329203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3269424</t>
+          <t>3271393</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3318599</t>
+          <t>3319099</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3367821</t>
+          <t>3368437</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3420679</t>
+          <t>3420971</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6653216</t>
+          <t>6652824</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6720313</t>
+          <t>6725378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26478</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279294</t>
+          <t>278716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290315</t>
+          <t>291062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269855</t>
+          <t>270374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284730</t>
+          <t>284688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555986</t>
+          <t>555094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574225</t>
+          <t>573296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485507</t>
+          <t>486125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495788</t>
+          <t>496014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500898</t>
+          <t>501197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516458</t>
+          <t>516557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>991109</t>
+          <t>990805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1010189</t>
+          <t>1010354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22853</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302298</t>
+          <t>302998</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313790</t>
+          <t>313895</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323614</t>
+          <t>323859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334172</t>
+          <t>334185</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631285</t>
+          <t>630908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646145</t>
+          <t>646338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357563</t>
+          <t>358330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366420</t>
+          <t>366426</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364160</t>
+          <t>363034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381838</t>
+          <t>382181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728118</t>
+          <t>726692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746520</t>
+          <t>746792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204236</t>
+          <t>205342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208271</t>
+          <t>208996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216717</t>
+          <t>216724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418483</t>
+          <t>417560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427004</t>
+          <t>426955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248195</t>
+          <t>248059</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258339</t>
+          <t>258212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246965</t>
+          <t>247083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263560</t>
+          <t>264286</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501309</t>
+          <t>500208</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520028</t>
+          <t>519516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>37048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>66406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618763</t>
+          <t>618460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639980</t>
+          <t>639810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>650395</t>
+          <t>649777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>671516</t>
+          <t>671893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277037</t>
+          <t>1278364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307562</t>
+          <t>1307152</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33947</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62177</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744890</t>
+          <t>744576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763626</t>
+          <t>764164</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>788497</t>
+          <t>788286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>810490</t>
+          <t>811012</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1542573</t>
+          <t>1540544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570803</t>
+          <t>1570594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>66300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>100996</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87941</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132776</t>
+          <t>132928</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>158996</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>218791</t>
+          <t>221779</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3284313</t>
+          <t>3284507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3320940</t>
+          <t>3319009</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3406804</t>
+          <t>3406652</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3451639</t>
+          <t>3451684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6706099</t>
+          <t>6703111</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6765894</t>
+          <t>6762284</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>296847</t>
+          <t>305054</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289033</t>
+          <t>296894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303257</t>
+          <t>309851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273376</t>
+          <t>299286</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266493</t>
+          <t>292441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278430</t>
+          <t>304178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>570223</t>
+          <t>604340</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560635</t>
+          <t>595202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578258</t>
+          <t>611945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>43934</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55134</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>501322</t>
+          <t>512696</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489238</t>
+          <t>500614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508713</t>
+          <t>520298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>490839</t>
+          <t>520511</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482146</t>
+          <t>511907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497004</t>
+          <t>527471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>992161</t>
+          <t>1033207</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>978225</t>
+          <t>1018449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002847</t>
+          <t>1043812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23864</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>42517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42194</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64750</t>
+          <t>65821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>294395</t>
+          <t>294958</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285828</t>
+          <t>286870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301133</t>
+          <t>301305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>315877</t>
+          <t>322976</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306895</t>
+          <t>312619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324004</t>
+          <t>330058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>610272</t>
+          <t>617934</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598536</t>
+          <t>604699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621092</t>
+          <t>627636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39895</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35350</t>
+          <t>35808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50969</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68473</t>
+          <t>76454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>287136</t>
+          <t>343119</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272662</t>
+          <t>327052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295591</t>
+          <t>353998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>450170</t>
+          <t>394737</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440368</t>
+          <t>386153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460869</t>
+          <t>401753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>737305</t>
+          <t>737857</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>719801</t>
+          <t>718653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752918</t>
+          <t>750504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172653</t>
+          <t>199259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168472</t>
+          <t>194402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175456</t>
+          <t>202298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>250064</t>
+          <t>219800</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245077</t>
+          <t>215500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254330</t>
+          <t>223044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>422717</t>
+          <t>419059</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415551</t>
+          <t>413112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427487</t>
+          <t>423726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,22 +12412,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,27 +12487,27 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -12525,27 +12525,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>252981</t>
+          <t>254203</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246363</t>
+          <t>248121</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257812</t>
+          <t>258824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>233247</t>
+          <t>239791</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225408</t>
+          <t>231919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239247</t>
+          <t>245995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>486229</t>
+          <t>493994</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477624</t>
+          <t>484742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494009</t>
+          <t>501708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>30684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51532</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61554</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>95057</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>77938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101848</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>588979</t>
+          <t>677757</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572747</t>
+          <t>661676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599251</t>
+          <t>689003</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>806100</t>
+          <t>718930</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>787711</t>
+          <t>706963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>829749</t>
+          <t>729396</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1395079</t>
+          <t>1396687</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1371696</t>
+          <t>1377234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424152</t>
+          <t>1413806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33680</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38479</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52075</t>
+          <t>57874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915354</t>
+          <t>783202</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905873</t>
+          <t>775155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923639</t>
+          <t>789344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>692618</t>
+          <t>801320</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>684051</t>
+          <t>791932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699305</t>
+          <t>809342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1607973</t>
+          <t>1584522</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1594377</t>
+          <t>1571529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1622417</t>
+          <t>1595096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115599</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>174998</t>
+          <t>189508</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>157053</t>
+          <t>195052</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>225152</t>
+          <t>241052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>299741</t>
+          <t>346329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>389766</t>
+          <t>416088</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3309668</t>
+          <t>3370249</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3283720</t>
+          <t>3342161</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3343119</t>
+          <t>3392609</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3512291</t>
+          <t>3517351</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3485868</t>
+          <t>3494657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3553967</t>
+          <t>3540657</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6821959</t>
+          <t>6887600</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6779972</t>
+          <t>6851290</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6869997</t>
+          <t>6921049</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
